--- a/inst/extdata/datapapers.xlsx
+++ b/inst/extdata/datapapers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t xml:space="preserve">paperid</t>
   </si>
@@ -119,6 +119,12 @@
     <t xml:space="preserve">Thailand</t>
   </si>
   <si>
+    <t xml:space="preserve">https://doi.org/10.21227/3q8d-jw96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEEE DataPort</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;jats:p&gt;Sustainable water quality data are important for understanding historical variability and trends in river regimes, as well as the impact of industrial waste on the health of aquatic ecosystems. Sustainable water management practices heavily depend on reliable and comprehensive data, prompting the need for accurate monitoring and assessment of water quality parameters. This research describes a reconstructed daily water quality dataset that complements rare historical observations for six station points along the Chao Phraya River in Thailand. Internet of Things technology and a Eureka water probe sensor is used to collect and reconstruct the water quality dataset for the period from June 2022–February 2023, with Turbidity, Optical Dissolved Oxygen, Dissolved Oxygen Saturation, Spatial Conductivity, Acidity/Basicity, Total Dissolved Solids, Salinity, Temperature, Chlorophyll, and Depth as the recorded parameters from six different stations. The presented dataset comprises a total of 211,322 data points, which are separated into six CSV files. The dataset is then evaluated using the Long Short-Term Memory (LSTM) algorithm with a Mean Squared Error (MSE) of 0.0012256, and Root Mean Squared Error (RMSE) of 0.0350080. The proposed dataset provides valuable insights for researchers studying river ecosystems, supporting informed decision-making and sustainable water management practices.&lt;/jats:p&gt;</t>
   </si>
   <si>
@@ -149,6 +155,12 @@
     <t xml:space="preserve">Cabo Verde</t>
   </si>
   <si>
+    <t xml:space="preserve">https://doi.org/10.15468/gx8zn4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBIF</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;jats:p&gt;Vector-borne diseases, primarily those transmitted by mosquitoes, are a serious public health problem. Some, such as dengue, put half of the world’s population at risk. Combating these diseases requires multifaceted strategies, with vector surveillance and control playing key roles. Robust and predictive surveillance systems for vector-borne diseases, based on risk stratification, enable the implementation of appropriate interventions across time and space. Here, we present a collection of entomological, demographic, water and sanitation, and climatic data from Praia (Cabo Verde), a hotspot for mosquito-borne diseases. These data were collected from June to November 2022, at 40 sentinel points scattered across the urban area of Praia. They constitute a valuable source of information for developing predictive scenarios of arbovirus outbreak risk using statistical models applied to spatial and non-spatial indicators. These data demonstrate the utility of GBIF in transforming large volumes of occurrence data into valuable information for arbovirus surveillance and vector control.&lt;/jats:p&gt;</t>
   </si>
   <si>
@@ -173,6 +185,9 @@
     <t xml:space="preserve">Nora Escribano</t>
   </si>
   <si>
+    <t xml:space="preserve">https://doi.org/10.15470/gkiznu</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://creativecommons.org/licenses/by/4.0</t>
   </si>
   <si>
@@ -191,6 +206,12 @@
     <t xml:space="preserve">Dan Wang</t>
   </si>
   <si>
+    <t xml:space="preserve">https://doi.org/10.6084/m9.figshare.19158206.v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figshare</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;jats:title&gt;Abstract&lt;/jats:title&gt;&lt;jats:p&gt;Wastewater treatment plants (WWTPs) alleviate water pollution but also induce resource consumption and environmental impacts especially greenhouse gas (GHG) emissions. Mitigating GHG emissions of WWTPs can contribute to achieving carbon neutrality in China. But there is still a lack of a high-resolution and time-series GHG emission inventories of WWTPs in China. In this study, we construct a firm-level emission inventory of WWTPs for CH&lt;jats:sub&gt;4&lt;/jats:sub&gt;, N&lt;jats:sub&gt;2&lt;/jats:sub&gt;O and CO&lt;jats:sub&gt;2&lt;/jats:sub&gt; emissions from different wastewater treatment processes, energy consumption and effluent discharge for the time-period from 2006 to 2019. We aim to develop a transparent, verifiable and comparable WWTP GHG emission inventory to support GHG mitigation of WWTPs in China.&lt;/jats:p&gt;</t>
   </si>
   <si>
@@ -209,6 +230,12 @@
     <t xml:space="preserve">Carolina Oliveira de Santana</t>
   </si>
   <si>
+    <t xml:space="preserve">https://doi.org/10.5061/dryad.2z34tmpp7; https://www.ncbi.nlm.nih.gov/sra/?term=SRP221580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dryad</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;jats:title&gt;Abstract&lt;/jats:title&gt;&lt;jats:p&gt;Wastewater treatment plant (WWTP) discharges alter water quality and microbial communities by introducing human-associated bacteria in the environment and by altering microbial communities. To fully understand this impact, it is crucial to study whether WWTP discharges affect water and sediments microbial communities in comparable ways and whether such effects depend on specific environmental variables. Here, we present a dataset investigating the impact of a WWTP on water quality and bacterial communities by comparing samples collected directly from the WWTP outflow to surface waters and sediments at two sites above and two sites below it over a period of five months. When possible, we measured five physicochemical variables (e.g., temperature, turbidity, conductivity, dissolved oxygen, and salinity), four bioindicators (e.g., &lt;jats:italic&gt;Escherichia coli&lt;/jats:italic&gt;, total coliforms, &lt;jats:italic&gt;Enterococcus&lt;/jats:italic&gt; sp., and endotoxins), and two molecular indicators (e.g., &lt;jats:italic&gt;intI1&lt;/jats:italic&gt;’s relative abundance, and &lt;jats:italic&gt;16S rRNA&lt;/jats:italic&gt; gene profiling). Preliminary results suggest that bioindicators correlate with environmental variables and that bacterial communities present in the water tables, sediments, and treated water differ greatly in composition and structure.&lt;/jats:p&gt;</t>
   </si>
   <si>
@@ -224,6 +251,12 @@
     <t xml:space="preserve">Ashraf Al-Ashhab</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.ncbi.nlm.nih.gov/bioproject/PRJNA488159; https://www.ncbi.nlm.nih.gov/bioproject/PRJNA497963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCBI/EBI</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;jats:title&gt;Abstract&lt;/jats:title&gt;&lt;jats:p&gt;Freshwater bodies are critical components of terrestrial ecosystems. The microbial communities of freshwater ecosystems are intimately linked water quality. These microbes interact with, utilize and recycle inorganic elements and organic matter. Here, we present three metagenomic sequence datasets (total of 182.9 Gbp) from different freshwater environments in Israel. The first dataset is from diverse freshwater bodies intended for different usages – a nature reserve, irrigation and aquaculture facilities, a tertiary wastewater treatment plant and a desert rainfall reservoir. The second represents a two-year time-series, collected during 2013–2014 at roughly monthly intervals, from a water reservoir connected to an aquaculture facility. The third is from several time-points during the winter and spring of 2015 in Lake Kinneret, including a bloom of the cyanobacterium Microcystis sp. These datasets are accompanied by physical, chemical, and biological measurements at each sampling point. We expect that these metagenomes will facilitate a wide range of comparative studies that seek to illuminate new aspects of freshwater microbial ecosystems and inform future water quality management approaches.&lt;/jats:p&gt;</t>
   </si>
   <si>
@@ -237,6 +270,12 @@
   </si>
   <si>
     <t xml:space="preserve">Anna Sofia Lippolis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zenodo.org/communities/whow; https://doi.org/10.5281/zenodo.14505948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenodo</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;jats:title&gt;Abstract&lt;/jats:title&gt;
@@ -715,17 +754,21 @@
       <c r="K3" t="s">
         <v>34</v>
       </c>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
       <c r="N3" t="s">
         <v>26</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R3" s="1" t="n">
         <v>46226</v>
@@ -736,19 +779,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>2025</v>
@@ -757,25 +800,29 @@
         <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4"/>
-      <c r="M4"/>
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
       <c r="N4" t="s">
         <v>26</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>46226</v>
@@ -786,19 +833,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>2018</v>
@@ -807,21 +854,25 @@
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O5"/>
       <c r="P5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>46226</v>
@@ -832,19 +883,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
         <v>2022</v>
@@ -853,21 +904,25 @@
         <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
+      <c r="L6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" t="s">
+        <v>65</v>
+      </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O6"/>
       <c r="P6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R6" s="1" t="n">
         <v>46226</v>
@@ -878,19 +933,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
         <v>2022</v>
@@ -899,21 +954,25 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
+      <c r="L7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" t="s">
+        <v>73</v>
+      </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Q7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>46226</v>
@@ -924,19 +983,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
         <v>2022</v>
@@ -945,21 +1004,25 @@
         <v>13</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
+      <c r="L8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" t="s">
+        <v>80</v>
+      </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Q8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>46226</v>
@@ -970,19 +1033,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
         <v>2025</v>
@@ -991,21 +1054,25 @@
         <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="J9"/>
       <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
+      <c r="L9" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" t="s">
+        <v>87</v>
+      </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>46226</v>
